--- a/Configs/Localization/本地化.xlsx
+++ b/Configs/Localization/本地化.xlsx
@@ -1,10 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:dbsheet="http://web.wps.cn/et/2021/dbsheet">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:dbsheet="http://web.wps.cn/et/2021/dbsheet" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="P:\Godot-Project\StartFromZero\Configs\Localization\"/>
+    </mc:Choice>
+  </mc:AlternateContent>
   <bookViews>
-    <workbookView windowWidth="27930" windowHeight="12975"/>
+    <workbookView windowHeight="17500" activeTab="1"/>
   </bookViews>
   <sheets>
     <sheet name="ChineseSimplified" sheetId="1" r:id="rId1"/>
@@ -85,37 +90,25 @@
     <t>值</t>
   </si>
   <si>
-    <t>MonsterSurviver</t>
+    <t>MenuForm.GameName</t>
   </si>
   <si>
     <t>怪物幸存者</t>
   </si>
   <si>
-    <t>MoveRule</t>
-  </si>
-  <si>
-    <t>WASD移动角色</t>
-  </si>
-  <si>
-    <t>StartGame</t>
+    <t>MenuForm.ExitGame</t>
+  </si>
+  <si>
+    <t>退出游戏</t>
+  </si>
+  <si>
+    <t>MenuForm.StartGame</t>
   </si>
   <si>
     <t>开始游戏</t>
   </si>
   <si>
-    <t>MainForm.Score</t>
-  </si>
-  <si>
-    <t>分数:</t>
-  </si>
-  <si>
-    <t>MainForm.Timer</t>
-  </si>
-  <si>
-    <t>计时:</t>
-  </si>
-  <si>
-    <t>SettingForm.Setting</t>
+    <t>MenuForm.Setting</t>
   </si>
   <si>
     <t>设置</t>
@@ -124,37 +117,49 @@
     <t>SettingForm.Music</t>
   </si>
   <si>
-    <t>音乐</t>
+    <t>音乐：</t>
   </si>
   <si>
     <t>SettingForm.Effect</t>
   </si>
   <si>
-    <t>音效</t>
+    <t>音效：</t>
+  </si>
+  <si>
+    <t>SettingForm.Language</t>
+  </si>
+  <si>
+    <t>语言：</t>
+  </si>
+  <si>
+    <t>SettingForm.Close</t>
+  </si>
+  <si>
+    <t>关闭</t>
   </si>
   <si>
     <t>Monster Surviver</t>
   </si>
   <si>
-    <t>WASD To Move Character</t>
+    <t>ExitGame</t>
   </si>
   <si>
     <t>Start</t>
   </si>
   <si>
-    <t>Score:</t>
-  </si>
-  <si>
-    <t>Timer:</t>
-  </si>
-  <si>
     <t>Setting</t>
   </si>
   <si>
-    <t>Music</t>
-  </si>
-  <si>
-    <t>Effect</t>
+    <t xml:space="preserve">Music: </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Effect: </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Language: </t>
+  </si>
+  <si>
+    <t>Close</t>
   </si>
 </sst>
 </file>
@@ -1168,10 +1173,10 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
   <dimension ref="A1:AJ16"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.25"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14"/>
   <cols>
-    <col min="1" max="1" width="9.225" customWidth="1"/>
-    <col min="2" max="2" width="6.75" customWidth="1"/>
+    <col min="1" max="1" width="13.8333333333333" customWidth="1"/>
+    <col min="2" max="2" width="13.25" customWidth="1"/>
     <col min="3" max="3" width="21.6666666666667" customWidth="1"/>
     <col min="4" max="4" width="48.1666666666667" customWidth="1"/>
     <col min="5" max="5" width="12.3833333333333" customWidth="1"/>
@@ -1472,7 +1477,7 @@
       <c r="B10">
         <v>5</v>
       </c>
-      <c r="C10" t="s">
+      <c r="C10" s="3" t="s">
         <v>20</v>
       </c>
       <c r="D10" t="s">
@@ -1488,7 +1493,7 @@
       <c r="B11">
         <v>6</v>
       </c>
-      <c r="C11" t="s">
+      <c r="C11" s="3" t="s">
         <v>22</v>
       </c>
       <c r="D11" t="s">
@@ -1577,9 +1582,12 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
   <dimension ref="A1:N13"/>
-  <sheetFormatPr defaultColWidth="15.1666666666667" defaultRowHeight="14.25"/>
+  <sheetFormatPr defaultColWidth="15.1666666666667" defaultRowHeight="14"/>
   <cols>
-    <col min="1" max="16384" width="15.1666666666667" customWidth="1"/>
+    <col min="1" max="2" width="15.1666666666667" customWidth="1"/>
+    <col min="3" max="3" width="21" customWidth="1"/>
+    <col min="4" max="4" width="23.25" customWidth="1"/>
+    <col min="5" max="16384" width="15.1666666666667" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:14">
@@ -1708,7 +1716,7 @@
       <c r="B10">
         <v>5</v>
       </c>
-      <c r="C10" t="s">
+      <c r="C10" s="3" t="s">
         <v>20</v>
       </c>
       <c r="D10" t="s">
@@ -1724,7 +1732,7 @@
       <c r="B11">
         <v>6</v>
       </c>
-      <c r="C11" t="s">
+      <c r="C11" s="3" t="s">
         <v>22</v>
       </c>
       <c r="D11" t="s">
